--- a/Excel/6_AgriculturalResidue_WIP_v03.xlsx
+++ b/Excel/6_AgriculturalResidue_WIP_v03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A838B0-79C0-45A5-A1C3-5B2520963140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5529C22F-B385-438D-8C62-A80EE954C8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="17280" firstSheet="5" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="27090" windowHeight="15075" firstSheet="8" activeTab="8" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -562,6 +562,10 @@
     <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
     <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
     <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
+    <definedName name="M1_Table_E_N2O">'6.3.1.1-2 Leaching and runoff'!$N$44:$O$46</definedName>
+    <definedName name="M1_Table_E_N2O_Consumer_1">'6.3.1.1-2 Leaching and runoff'!$D$44:$E$46</definedName>
+    <definedName name="M1_Table_M_leach_cp">'6.3.1.1-2 Leaching and runoff'!$D$23:$I$25</definedName>
+    <definedName name="M2_Table_M_leach_cp">'6.3.1.1-2 Leaching and runoff'!$N$23:$S$23</definedName>
     <definedName name="Range_LivestockStartingValues">#REF!</definedName>
     <definedName name="Step1">#REF!</definedName>
     <definedName name="Step2">#REF!</definedName>
@@ -14460,7 +14464,7 @@
         <v>Constant</v>
       </c>
       <c r="I18" s="117">
-        <f>'Input - Crop'!$E$43</f>
+        <f>X_Cell_Crop_PercentResidueBurned</f>
         <v>0.3</v>
       </c>
     </row>
@@ -24154,11 +24158,11 @@
         <v>217</v>
       </c>
       <c r="E9" s="125">
-        <f>'6.1.1.1-2 Crop residue N2O'!E42</f>
+        <f>VEERG_6_1_1_1__1__NitrousOxideEmissionsFromCropResidues_Result_Method1</f>
         <v>2.3377199999999997E-2</v>
       </c>
       <c r="F9" s="125">
-        <f>'6.1.1.1-2 Crop residue N2O'!N77</f>
+        <f>VEERG_6_1_1_1__1__NitrousOxideEmissionsFromCropResidues_Result_Method2</f>
         <v>2.3377199999999997E-2</v>
       </c>
       <c r="G9" s="52" t="s">
@@ -24187,11 +24191,11 @@
         <v>218</v>
       </c>
       <c r="E10" s="144">
-        <f>'6.2.1.1-2 Pasture residue N2O'!E40</f>
+        <f>VEERG_6_2_1_1__1__NitrousOxideEmissionsFromPastureResidues_Result_Method1</f>
         <v>5.8320428571428569E-7</v>
       </c>
       <c r="F10" s="144">
-        <f>'6.2.1.1-2 Pasture residue N2O'!O40</f>
+        <f>VEERG_6_2_1_1__1__NitrousOxideEmissionsFromPastureResidues_Result_Method2</f>
         <v>5.8320428571428569E-7</v>
       </c>
       <c r="G10" s="52" t="s">
@@ -24216,11 +24220,11 @@
         <v>219</v>
       </c>
       <c r="E11" s="125">
-        <f>'6.3.1.1-2 Leaching and runoff'!E48</f>
+        <f>VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_Result_Method1</f>
         <v>1.2343469531862857E-2</v>
       </c>
       <c r="F11" s="125">
-        <f>'6.3.1.1-2 Leaching and runoff'!O48</f>
+        <f>VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_Result_Method2</f>
         <v>1.2343469531862857E-2</v>
       </c>
       <c r="G11" s="52" t="s">
@@ -24248,7 +24252,7 @@
         <v>220</v>
       </c>
       <c r="E12" s="125">
-        <f>'6.4.1.1-2 Residue burning'!E39</f>
+        <f>VEERG_6_4_1_1__2__NitrousOxideEmissionsFromBurningOfCropResidues_Result_Method1</f>
         <v>4.4692560000000004E-3</v>
       </c>
       <c r="F12" s="125">
@@ -24281,7 +24285,7 @@
         <v>220</v>
       </c>
       <c r="E13" s="125">
-        <f>'6.4.1.1-2 Residue burning'!E62</f>
+        <f>VEERG_6_4_1_1__1__MethaneEmissionsFromBurningOfCropResidues_Result_Method1</f>
         <v>0.116424</v>
       </c>
       <c r="F13" s="125">
@@ -28854,7 +28858,7 @@
         <v>Input</v>
       </c>
       <c r="T14" s="117">
-        <f>'Input - Pasture'!$E$19</f>
+        <f>X_Cell_Pasture_YieldPerHectare</f>
         <v>8.34</v>
       </c>
     </row>
@@ -30070,15 +30074,15 @@
         <v>2975.2799999999997</v>
       </c>
       <c r="F24" s="50" t="str">
-        <f>'Input - Crop'!$E$11</f>
+        <f>X_Cell_Crop_IrrigationMethod</f>
         <v>Sprinkler irrigation</v>
       </c>
       <c r="G24" s="50" t="str">
-        <f>'Input - Site'!E$23</f>
+        <f>X_Cell_Site_LeachingZone</f>
         <v>NO - Not in leaching zone</v>
       </c>
       <c r="H24" s="50">
-        <f>CommonCropping_InputFunctions.CommonCropping_GetFracWET(G24,F24,#REF!,#REF!, Table_SourceData_FracWETIrrigation[Irrigation type i],Table_SourceData_FracWETIrrigation[FracWET])</f>
+        <f>CommonCropping_InputFunctions.CommonCropping_GetFracWET(G24,F24,Table_SourceData_FracWET[Is in leaching zone],Table_SourceData_FracWET[FracWET], Table_SourceData_FracWETIrrigation[Irrigation type i],Table_SourceData_FracWETIrrigation[FracWET])</f>
         <v>1</v>
       </c>
       <c r="I24" s="50" cm="1">
@@ -30107,15 +30111,15 @@
         <v>7.4226E-2</v>
       </c>
       <c r="F25" s="50" t="str">
-        <f>'Input - Pasture'!$E$10</f>
+        <f>X_Cell_Pasture_IrrigationMethod</f>
         <v>Surface irrigation</v>
       </c>
       <c r="G25" s="50" t="str">
-        <f>'Input - Site'!E$23</f>
+        <f>X_Cell_Site_LeachingZone</f>
         <v>NO - Not in leaching zone</v>
       </c>
       <c r="H25" s="50">
-        <f>CommonCropping_InputFunctions.CommonCropping_GetFracWET(G25,F25,#REF!,#REF!, Table_SourceData_FracWETIrrigation[Irrigation type i],Table_SourceData_FracWETIrrigation[FracWET])</f>
+        <f>CommonCropping_InputFunctions.CommonCropping_GetFracWET(G25,F25,Table_SourceData_FracWET[Is in leaching zone],Table_SourceData_FracWET[FracWET], Table_SourceData_FracWETIrrigation[Irrigation type i],Table_SourceData_FracWETIrrigation[FracWET])</f>
         <v>1</v>
       </c>
       <c r="I25" s="50" cm="1">
@@ -30772,26 +30776,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAJwBcACIAIAAmACAAcwBoACAAJgAgAFwAIgAnACEAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAJgAgAFwAIgAgAFwAIgAgACYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBQAHIAbwBkAHUAYwB0AEwAbwBvAGsAdQBwAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABQAHIAbwBkAHUAYwB0ACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5AEgAZQBhAGQAZQByAHMALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkASABlAGEAZABlAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAXAAiAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEALABcAG4AIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABbAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADIAXQAsAFwAbgAgACAAWwBMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwAXABuACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACAAPQAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADEALABcAG4AIAAgACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAgAD0AIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACAAKgAgAGMAcgBpAHQAZQByAGkAYQAyACAAKgAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0ACwAXABuACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0AFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEEAcABwAGwAaQBlAGQAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADYAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANABcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA1AFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA1AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA0ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQAgAD0AIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgAFwAIgBHAGwAbwBiAGEAbABcACIALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA0ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBHAGUAdABTAGMAbwBwAGUAMwBFAEYAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgAFMAYwBvAHAAZQAzAEEAcgByAGEAeQAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgAFMAbwB1AHIAYwBlAFIAbwB3ACwAXABuACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIABTAGMAbwBwAGUAMwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEMAbwBsAHUAbQBuACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAE0AQQBUAEMASAAoAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQBSAG8AdwAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHIAcgBhAHkALABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQwBvAGwAdQBtAG4ALABcAG4AIAAgAEUAbABlAG0AZQBuAHQAUgBvAHcALABcAG4AIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAATQBBAFQAQwBIACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAIAAgACAAIABFAGwAZQBtAGUAbgB0AFIAbwB3ACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQQBjAHQAaQB2AGUASQBuAGcAcgBlAGQAaQBlAG4AdABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABJAEYAKABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEAIAA9ACAAXAAiAFAAZQByAGMAZQBuAHQAIABvAGYAIABwAHIAbwBkAHUAYwB0AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAxACAAPQAgAFwAIgBQAGUAcgBjAGUAbgB0ACAAbwBmACAAcAByAG8AZAB1AGMAdABcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEkARgAoAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMQAgAD0AIABcACIAUABlAHIAYwBlAG4AdAAgAG8AZgAgAHAAcgBvAGQAdQBjAHQAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMQAgAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBmAH0AKAAoAE0ATgBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagAsAE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AXwBqAGYAXABuAEUARgBfAGoATgAyAE8AXABuAEMAXwBOADIATwBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABFAEYAXwBqAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAZgAgACoAIABFAEYAXwBqAE4AMgBPACAAKgAgAEMAXwBOADIATwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoALABOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAxAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBOADIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADEALgAxAC4AMgAgACgAMQApACgAMgApACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AXwBqAGYAXABuAGsAZwAgAE4AXABuAHsATQBOAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBpAG4AbwByAGcAYQBuAGkAYwAsAGYAfQBcAG4AVABNAF8AagBmAFwAbgBGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBpAG4AbwByAGcAYQBuAGkAYwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AE0ATgB9AF8AewBqAGYAfQA9AFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYATgBfAHsAaQBuAG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALABcACIAdABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAcgByAGkAZwBhAHQAZQBkACAAbQBhAGkAegBlAFwAbgBFAEYAXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAE4AMgBPAFwAbgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcAG4ARQBGAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUALABOADIATwB9AD0AKAAtADAALgAxADQANwA0ACsAKAAwAC4AMAAwADYAMQBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AaQByAHIAaQBnAGEAdABlAGQAbQBhAGkAegBlAH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9AFwAbgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQAsAFwAbgAgACAAIAAgACgALQAwAC4AMQA0ADcANAAgACsAIAAoADAALgAwADAANgAxACAAKgAgAE4AXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGYAagBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADIALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AGkAcgByAGkAZwBhAHQAZQBkAG0AYQBpAHoAZQAsAE4AMgBPAH0APQAoAC0AMAAuADEANAA3ADQAKwAoADAALgAwADAANgAxAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABnAHIAYQBpAG4AcwAgAGkAbgAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAbgBFAEYAXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4ATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMALABcAG4AIAAgACAAIAAoADAALgAwADcAOAAxACAAKwAgACgAMAAuADAAMAA3ADUAIAAqACAATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwApACkAIAAqACAAMQAwACAAXgAgAC0AMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAZwByAGEAaQBuAHMAIABpAG4AIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgBqAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABnAHIAYQBpAG4AcwAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAbgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AGMAbwB0AHQAbwBuACwATgAyAE8AfQA9AFwAXABtAGkAbgBcAFwAbABlAGYAdAAoACgAMAAuADAAMQBcAFwAdABpAG0AZQBzACgAMAAuADIAOQArADAALgAwADAANwBcAFwAdABpAG0AZQBzACgAKABlAF4AewAoADAALgAwADMANwBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AYwBvAHQAdABvAG4AfQApAH0ALQAxACkALwBOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9ACkAKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9ACwAMAAuADAAMQA4ADMAXABcAHIAaQBnAGgAdAApAFwAbgBOAF8AZgBqAEMAbwB0AHQAbwBuAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGYAagBDAG8AdAB0AG8AbgAsAFwAbgAgACAAIAAgACgAMAAuADAAMQAgACoAIAAoADAALgAyADkAIAArACAAKAAgACAAKAAwAC4AMAAwADcAIAAqACAAKABFAFgAUAAoADAALgAwADMANwAgACoAIABOAF8AZgBqAEMAbwB0AHQAbwBuACkAIAAtACAAMQApACkAIAAvACAATgBfAGYAagBDAG8AdAB0AG8AbgAgACAAKQAgACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAZgBqAD0AYwBvAHQAdABvAG4ALABOADIATwB9AD0AKAAwAC4AMAAxACAAXABcAHQAaQBtAGUAcwAgACgAMAAuADIAOQAgACsAIABcAFwAZgByAGEAYwB7ADAALgAwADAANwAoAGUAXgB7ADAALgAwADMANwAgAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9AH0ALQAxACkAfQB7AE4AXwB7AGYAagA9AGMAbwB0AHQAbwBuAH0AfQApACkAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBmAGoAQwBvAHQAdABvAG4AXAAiACwAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGkAbgAgAHQAaABlACAAYwBvAHQAdABvAG4AIABjAHIAbwBwAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQA6ACAARgBlAHIAdABpAGwAaQBzAGUAcgAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUALgAxACAASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcAG4ARQBfAEMATwAyAFwAbgB0ACAAQwBPADIAXABuAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AVQBfAGoAZgBcAG4ARQBGAF8AdQByAGUAYQBDAE8AMgBcAG4AQwBfAEMATwAyAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAFUAXwBqAGYALAAgAEUARgBfAHUAcgBlAGEAQwBPADIALAAgAEMAXwBDAE8AMgAsAFwAbgAgACAAIAAgACgATQBVAF8AagBmACAAKgAgAEUARgBfAHUAcgBlAGEAQwBPADIAIAAqACAAQwBfAEMATwAyACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBVAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAAdQByAGUAYQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwB1AHIAZQBhAEMATwAyAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBhAHIAYgBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAIAB1AHIAZQBhAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAEMATwAyAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABjAGEAcgBiAG8AbgAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQBhAHMAcwAgAG8AZgAgAHUAcgBlAGEAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAFUAXwBqAGYAXABuAGsAZwAgAHUAcgBlAGEAXABuAHsATQBVAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBVAF8AZgBcAG4AVABNAF8AagBmAFwAbgBGAFUAXwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBVAF8AZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAFUAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIAB1AHIAZQBhACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AVQBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIAB1AHIAZQBhAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBNAFUAfQBfAHsAagBmAH0APQBUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAFUAXwBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAF8AagBmAFwAIgAsAFwAIgB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBVAF8AZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdQByAGUAYQAgAGkAbgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALABcACIAawBnACAAdQByAGUAYQAvAGsAZwBcACIALAAgAFwAIgBMAG8AbwBrAHUAcABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMgAgAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8ALABpAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARQBGAF8ATgAyAE8AaQBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBpAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABFAEYAXwBOADIATwBpACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBTAG8AaQBsAF8AagBmACAAKgAgAEUARgBfAE4AMgBPAGkAIAAqACAAQwBfAE4AMgBPACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBOAFMAbwBpAGwAXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAaQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABhAG4AZAAgAGEAcQB1AGEAdABpAGMAIABzAHkAcwB0AGUAbQBzACAAaQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAXAAiAFcAZQB0ACAAbwByACAAZAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXABuAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARgBOAF8AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbwByAGcAYQBuAGkAYwBqAGYALAAgAEYATgBfAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABGAE4AXwBvAHIAZwBhAG4AaQBjAGYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAG8AcgBnAGEAbgBpAGMAagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYATgBfAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIATwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMwAgAEwAaQBtAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAG4AZAAgAGQAbwBsAG8AbQBpAHQAZQAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8AbABpAG0AZQBcAG4AdAAgAEMATwAyAFwAbgBFAF8AewBsAGkAbQBlAH0APQBbACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwAaQBtAGUAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGkAbQBlAH0AKQArACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEQAbwBsAFwAXAB0AGkAbQBlAHMAIABQAF8AewBkAG8AbAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGQAbwBsAH0AKQBdAFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAE8AMgB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBNAF8AbABpAG0AZQBcAG4ARgByAGEAYwBMAGkAbQBlAFwAbgBQAF8AbABpAG0AZQBcAG4ARQBGAF8AbABpAG0AZQBcAG4ARgByAGEAYwBEAG8AbABcAG4AUABfAGQAbwBsAFwAbgBFAEYAXwBkAG8AbABcAG4AQwBfAEMATwAyAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABpAG0AZQAsACAARgByAGEAYwBMAGkAbQBlACwAIABQAF8AbABpAG0AZQAsACAARQBGAF8AbABpAG0AZQAsACAARgByAGEAYwBEAG8AbAAsACAAUABfAGQAbwBsACwAIABFAEYAXwBkAG8AbAAsACAAQwBfAEMATwAyACwAXABuACAAIAAgACAAKAAoAE0AXwBsAGkAbQBlACAAKgAgAEYAcgBhAGMATABpAG0AZQAgACoAIABQAF8AbABpAG0AZQAgACoAIABFAEYAXwBsAGkAbQBlACkAIAArACAAKABNAF8AbABpAG0AZQAgACoAIABGAHIAYQBjAEQAbwBsACAAKgAgAFAAXwBkAG8AbAAgACoAIABFAEYAXwBkAG8AbAApACkAIAAqACAAQwBfAEMATwAyACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbABpAG0AZQAgAGEAbgBkACAAZABvAGwAbwBtAGkAdABlACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGwAaQBtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGwAaQBtAGUAfQA9AFsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABpAG0AZQBcAFwAdABpAG0AZQBzACAAUABfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAaQBtAGUAfQApACsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARABvAGwAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGQAbwBsAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZABvAGwAfQApAF0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMATwAyAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGwAaQBtAGUAXAAiACwAXAAiAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABsAGkAbQBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABsAGkAbQBlAHMAdABvAG4AZQAgACgAQwBhAEMATwAzACkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgBhAGwAIABwAHUAcgBpAHQAeQAgAG8AZgAgAGwAaQBtAGUAcwB0AG8AbgBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAaQBtAGUAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGkAbQBlAHMAdABvAG4AZQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAXAAiACwAIABcACIAawBnACAAQwAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARABvAGwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGQAbwBsAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZABvAGwAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAG8AbABvAG0AaQB0AGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8AQwBPADIAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADQAIABJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGYAcgBvAG0AIABhAGwAbAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIABhAG4AZAAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8AYQBkAGkAbgBvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAGkAbgBvAHIAZwBhAG4AaQBjAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYALAAgAEUARgBfAE4AMgBPAGoALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBhAGQAaQBuAG8AcgBnAGEAbgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAaQBuAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBqAH0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADQALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBqAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsAFwAIgByAGEAaQBuAGYAYQBsAGwAIAByAGUAZwBpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4AawBnACAATgBcAG4ATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AD0AewBNAE4AfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMARgBfAHsAZgB9AFwAbgBNAE4AXwBqAGYAXABuAEYAcgBhAGMARwBBAFMARgBfAGYAXABuAGoAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAsACAARgByAGEAYwBHAEEAUwBGAF8AZgAsAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAgACoAIABGAHIAYQBjAEcAQQBTAEYAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AHYAbwBsACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAEYAXwB7AGYAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMARgBfAGYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAaABhAHQAIAB2AG8AbABhAHQAaQBsAGkAcwBlAHMAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmACwAIABFAEYAXwBOADIATwBqACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAbwByAGcAYQBuAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGoAfQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgA0AC4AMQAuADMAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AagBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAXAAiACwAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmAFwAbgBrAGcAIABOAFwAbgBNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AE0ATgBTAG8AaQBsAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAF8AewBzAG8AaQBsAH0AXABuAE0ATgBTAG8AaQBsAF8AagBmAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsACwAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYAIAAqACAARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAdgBvAGwALABvAHIAZwBhAG4AaQBjACwAagBmAH0APQBNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAcwBvAGkAbAB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAFMAbwBpAGwAXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAyAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABOACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwBcACIALAAgAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADUAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAC0AbwBmAGYAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXABuAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBmAGUAcgB0ACwAbABlAGEAYwBoAH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoACgATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0AKwBNAF8AewBsAGUAYQBjAGgALABvAHIAZwBhAG4AaQBjACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAbgBNAF8AbABlAGEAYwBoAG8AcgBnAGEAbgBpAGMAagBcAG4ARQBGAF8AbABlAGEAYwBoAFwAbgBDAF8ATgAyAE8AXABuAGoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagAsACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAF8AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjAGoAIAArACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAKQAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGYAZQByAHQALABsAGUAYQBjAGgAfQA9AFwAXABzAHUAbQBfAHsAagB9ACgAKABNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQArAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAZQBhAGMAaABcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcAG4AawBnACAATgBcAG4ATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBXAEUAVAAsAGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsATABFAEEAQwBIAH0AKQBcAG4ATQBOAF8AagBmAFwAbgBGAHIAYQBjAFcARQBUAGoAXABuAEYAcgBhAGMATABFAEEAQwBIAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABGAHIAYQBjAFcARQBUAGoALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQBOAF8AagBmACAAKgAgAEYAcgBhAGMAVwBFAFQAagAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBmAH0AXABcAGwAZQBmAHQAKAB7AE0ATgB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcAG4ATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAFMAbwBpAGwAfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AFcARQBUACwAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBMAEUAQQBDAEgAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARgByAGEAYwBXAEUAVABqAFwAbgBGAHIAYQBjAEwARQBBAEMASABcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYALAAgAEYAcgBhAGMAVwBFAFQAagAsACAARgByAGEAYwBMAEUAQQBDAEgALABcAG4AIAAgACAAIABNAE4AUwBvAGkAbABfAGoAZgAgACoAIABGAHIAYQBjAFcARQBUAGoAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9AFwAXABsAGUAZgB0ACgAewBNAE4AUwBvAGkAbAB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AUwBvAGkAbABfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsAFwAIgBsAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAHAAdQByAHAAbwBzAGUAIABhAG4AZAAgAHkAaQBlAGwAZABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABwAHUAcgBwAG8AcwBlACAAYQBuAGQAIAB5AGkAZQBsAGQAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAOAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAcgBwAG8AcwBlAFwAIgAsACAAXAAiAFAAZQByACAAaABlAGMAdABhAHIAZQAgAHUAbgBpAHQAXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAHQAZQByAG0AXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAGUAbgBkAHAAbwBpAG4AdABcACIALAAgAFwAIgBIAGEAcgB2AGUAcwB0ACAAdQBpAHQAXAAiACwAIABcACIAWQBpAGUAbABkACAAbgBvAHQAZQBcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAG4AbwB0AGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG4AbwB0AGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHMAaAAgAGcAcgBhAGkAbgAgAGMAcgBvAHAAXAAiACwAIABcACIAZwByAGEAaQBuAFwAIgAsACAAXAAiAHkAaQBlAGwAZABcACIALAAgAFwAIgBoAGEAcgB2AGUAcwB0AFwAIgAsACAAXAAiAGcAcgBhAGkAbgBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAGcAcgBhAGkAbgAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgByAG8AbQAgAHQAaABlACAAcABsAGEAbgB0AFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAcAByAG8AdgBpAGQAZQBkACAAZgByAG8AbQAgAGQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwBcACIALAAgAFwAIgBUAG8AdABhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAaQBzACAAdABoAGUAIAB0AG8AdABhAGwAIABnAHIAYQBpAG4AIABoAGEAcgB2AGUAcwB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcwBoACAAYwByAG8AcAAgAGYAbwByACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAeQBpAGUAbABkAFwAIgAsACAAXAAiAGgAYQByAHYAZQBzAHQAXAAiACwAIABcACIAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgBvAHIAIABoAGEAeQAvAHMAaQBsAGEAZwBlAFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAMAAgAGEAcwBzAHUAbQBpAG4AZwAgAHQAaABlACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAaQBzACAAaABhAHIAdgBlAHMAdABlAGQAIABmAG8AcgAgAGgAYQB5AC8AcwBpAGwAYQBnAGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGkAcwAgAHQAaABlACAAdABvAHQAYQBsACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwAgAGgAYQByAHYAZQBzAHQAZQBkACAAYQBzACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBtAGEAcwBzAFwAIgAsACAAXAAiAGUAbgBkACAAbwBmACAAYwByAG8AcAAgAGMAeQBjAGwAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAWQBpAGUAbABkACAAaQBzACAAdABoAGUAIAB3AGgAbwBsAGUAIABwAGwAYQBuAHQAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGkAcwAgADEAIABhAHMAcwB1AG0AaQBuAGcAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGkAcwAgAGsAZQBwAHQAIABhAHMAIABjAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAFQAbwB0AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABpAHMAIAB0AGgAZQAgAHQAbwB0AGEAbAAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGIAaQBvAG0AYQBzAHMAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADEAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4AMQA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADkALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAUgBlAHMAaQBkAHUAZQA6ACAAQwByAG8AcAAgAHIAYQB0AGkAbwBcACIALAAgAFwAIgBCAGUAbABvAHcALQBnAHIAbwB1AG4AZAA6ACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAEMAYQByAGIAbwBuACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAZAByAHkAIABtAGEAdAB0AGUAcgBcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkAFwAIgAsACAAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAdABpAG0AZQAgAG8AZgAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAQgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAFIAQQBHAGMAXAAiACwAIABcACIAUgBCAEcAYwBcACIALAAgAFwAIgBEAE0AYwBcACIALAAgAFwAIgBDAEMAYwBcACIALAAgAFwAIgBOAEMAQQBHAGMAXAAiACwAIABcACIATgBDAEIARwBjAFwAIgAsACAAXAAiAFMAYwBcACIALAAgAFwAIgBaAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAMQAuADUAMAAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOQAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIAAxAC4AMgA0ACwAIAAwAC4AMwAyACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADcALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AMwA5ACwAIAAwAC4AOAA1ACwAIAAwAC4ANAAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANwAsACAAMQAuADAALAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAMQAuADQAMgAsACAAMAAuADQAMwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgADEALgAzADEALAAgADAALgAxADYALAAgADAALgA4ADAALAAgADAALgA0ADIALAAgADAALgAwADAANwAsACAAMAAuADAAMQAwACwAIAAxAC4AMAAsACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIAAxAC4ANQAwACwAIAAwAC4AMgAyACwAIAAwAC4AOAAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADgALAAgADAALgAwADAANwAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgADEALgA1ADAALAAgADAALgA0ADIALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIAAxAC4ANAA2ACwAIAAwAC4AMwA2ACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADYALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgADEALgAzADcALAAgADAALgA1ADEALAAgADAALgA4ADcALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIAAwAC4AMwA0ACwAIAAwAC4ANAAzACwAIAAwAC4AMgA1ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAyADAALAAgADAALgAwADEAMAAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIAAxAC4AMAA3ACwAIAAwAC4AMgAwACwAIAAwAC4AOAAwACwAIAAwAC4ANAAyACwAIAAwAC4AMAAxADYALAAgADAALgAwADEANAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADIANQAsACAAMAAuADQANQAsACAAMAAuADIAMAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADcALAAgADEALgAwACwAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIAAxAC4AOQAwACwAIAAwAC4AMwAwACwAIAAwAC4AOQAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgADEALgA1ADAALAAgADAALgAyADkALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgADIALgAwADgALAAgADAALgAzADMALAAgADAALgA5ADYALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAMQAuADMANAAsACAAMAAuADMANwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgADEALgAwADAALAAgADAALgAyADIALAAgADAALgA4ADUALAAgADAALgA0ADAALAAgADAALgAwADAAOAAsACAAMAAuADAAMAA5ACwAIABcACIAbgAvAGEAXAAiACwAIABcACIAbgAvAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIAAxAC4ANQAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAJwBOAC8AQQAnACAAdgBhAGwAdQBlAHMAIABwAGEAcwBzAGUAZAAgAGEAcwAgAHoAZQByAG8AIABmAG8AcgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBzAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBDAHIAbwBwACAAYQB0AHQAcgBpAGIAdQB0AGUAcwAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAAKABGAEYATwBEAGMAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADIAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAHIAbwBwACAAYQB0AHQAcgBpAGIAdQB0AGUAcwAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAAKABGAEYATwBEAGMAKQBcACIAKQApADsAXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgAyADoAIABDAHIAbwBwACAAYQB0AHQAcgBpAGIAdQB0AGUAcwAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAAKABGAEYATwBEAGMAKQBcACIAKQApADsAXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAARgBGAE8ARABjAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAEEAbABsACAAcwB0AGEAdABlAHMAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAEEAbABsACAAcwB0AGEAdABlAHMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AQwB1AHMAdABvAG0AaQBzAGUAZABEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANAA0ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAYwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIATgBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAUwBwAGwAaQB0ACAAJwBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAJwAgAGkAbgB0AG8AIABpAG4AZABpAHYAaQBkAHUAYQBsACAAYwByAG8AcAAgAHQAeQBwAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAHMAdABhAHQAZQAuACAATABpAHMAdABlAGQAIABhAGwAbAAgAHMAdABhAHQAZQBzACAAZgBvAHIAIABTAHUAZwBhAHIAIABDAGEAbgBlACwAIAB3AGkAdABoACAAJwBOAC8AQQAnACAAZgBvAHIAIABzAHQAYQB0AGUAcwAgAHcAaABlAHIAZQAgAGkAdAAgAGkAcwAgAG4AbwB0ACAAZwByAG8AdwBuAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUABhAHMAdAB1AHIAZQAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAIABQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAOgAgAFAAYQBzAHQAdQByAGUAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAAWQBpAGUAbABkACAAKAB0ACAARABNACAAaABhACkAIABZAHAAXAAiACwAIABcACIAQgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAOgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAFIAQgBHAHAAXAAiACwAIABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABBAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAE4AQwBBAEcAcABcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAEIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAATgBDAEIARwBwAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AbgB1AGEAbAAgAGcAcgBhAHMAcwBcACIALAAgADQALgA0ADEALAAgADAALgA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAYQBzAHMAIABjAGwAbwB2AGUAcgAgAG0AaQB4AHQAdQByAGUAXAAiACwAIAA4AC4AMwA0ACwAIAAwAC4AOAAsACAAMAAuADAAMgA1ACwAIAAwAC4AMAAxADYALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATAB1AGMAZQByAG4AZQBcACIALAAgADgALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADEAOQAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABsAGUAZwB1AG0AZQBcACIALAAgADUALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADIAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgBlAG4AbgBpAGEAbAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAA4AC4AMwA1ACwAIAAwAC4AOAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADIALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAIgApACkAOwBcAG4AXABuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAdQByAG4AaQBuAGcAIABvAGYAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHIAZQBzAGkAZAB1AGUAcwAgAC0AIABFAEYAcwBcACIAKQApADsAXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAdgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIAA1AC4AMwAxADoAIABCAHUAcgBuAGkAbgBnACAAbwBmACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIAByAGUAcwBpAGQAdQBlAHMAIAAtACAARQBGAHMAXAAiACkAKQA7AFwAbgBcAG4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzACAAcwBwAGUAYwBpAGUAcwBcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAEUARgBnACAAKABHAGcAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAcwBwAGUAYwBpAGUAcwAvACAARwBnACAAZQBsAGUAbQBlAG4AdAAgAGkAbgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAKQBcACIALAAgAFwAIgBFAGwAZQBtAGUAbgB0AGEAbAAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAQwBnACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAwAC4AMAAwADMANQAsACAAXAAiADEANgAvADEAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADAALgAwADAANwA2ACwAIABcACIANAA0AC8AMgA4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4ATwB4AFwAIgAsACAAMAAuADIAMQAwADAALAAgAFwAIgA0ADYALwAxADQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAMAAuADAANwA4ADAALAAgAFwAIgAyADgALwAxADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAMAAuADAAMAA5ADEALAAgAFwAIgAxADQALwAxADIAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANAAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAIABUAGEAYgBsAGUAIAAxADEALgAxACAAWwAxACwAIABwAC4AIAAxADEAXQBcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAXAAiACwAIABcACIARQBGACAAaQAgAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ARQBcAG4AdAAgAE4AMgBPAFwAbgBFAD0AXABcAHMAdQBtAF8AewBjAH0AewBNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQB9AFwAbgBNAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIABjACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBnAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBjACwAIABFAEYAXwBOAGkALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0AXwBjACAAKgAgAEUARgBfAE4AaQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAHIAbwBwAHMAIABjACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAbABlAGYAdAAoAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAYwAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADEALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAVwBlAHQAIABvAHIAIABkAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAGMAXABuAGsAZwAgAE4AXABuAE0AXwB7AGMAfQA9ACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAYwB9AC0ARgBGAE8ARABfAHsAYwB9ACkAXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AKQArACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBCAEcAYwB9ACkAXABuAFAAYwAgAD0AIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACkAXABuAFIAQQBHAGMAIAA9ACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAFIAQgBHAGMAIAA9ACAAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAEYATwBEAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBEAE0AYwAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAKQBcAG4ATgBDAEEARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ATgBDAEIARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAXwBjACwAIABSAF8AQQBHAGMALAAgAEYAXwBjACwAIABGAEYATwBEAF8AYwAsACAARABNAF8AYwAsACAATgBDAF8AQQBHAGMALAAgAFIAXwBCAEcAYwAsACAATgBDAF8AQgBHAGMALABcAG4AIAAgACAAIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwAgACoAIAAoADEAIAAtACAARgBfAGMAIAAtACAARgBGAE8ARABfAGMAKQAgACoAIABEAE0AXwBjACAAKgAgAE4AQwBfAEEARwBjACkAIAArACAAKABQAF8AYwAgACoAIABSAF8AQQBHAGMAIAAqACAAUgBfAEIARwBjACAAKgAgAEQATQBfAGMAIAAqACAATgBDAF8AQgBHAGMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYwB9AD0AKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBjAH0ALQBGAEYATwBEAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQApACsAKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBjAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQgBHAGMAXAAiACwAXAAiAGIAZQBsAG8AdwAgAGcAcgBvAHUAbgBkAC0AcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAF8AYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AXwBjAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEEARwBjAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADAALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAXwBjAFwAIgAsAFwAIgBhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQQBHAGMAXAAiACwAXAAiAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBCAEcAYwBcACIALABcACIAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAxAC4AMQAuADIAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAF8AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQgBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsAFwAIgBTAHQAYQB0AGUAIABvAHIAIAB0AGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcAG4ARgBGAE8ARABjAGIAYQBsAGUAZABcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4ARgBGAE8ARABfAHsAYwB9AD0AXABcAGYAcgBhAGMAewBCAFwAXAB0AGkAbQBlAHMAIABNAF8AewBCAH0AfQB7AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHACwAYwB9AH0AXABuAEIAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBNAEIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAGUAYQBjAGgAIABiAGEAbABlACAAKABrAGcAKQBcAG4AUABjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcAG4AUgBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABCACwAIABNAF8AQgAsACAAUABfAGMALAAgAFIAXwBBAEcAYwAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAoAEIAIAAqACAATQBfAEIAKQAgAC8AIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwApACwAIAAwACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjACwAIABjAGEAbABjAHUAbABhAHQAZQBkACAAdwBoAGUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAYQByAGUAIABiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMALABiAGEAbABlAGQAfQA9AFwAXABmAHIAYQBjAHsAQgBcAFwAdABpAG0AZQBzACAATQBfAHsAQgB9AH0AewBQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwAsAGMAfQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBcACIALABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBCAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAZQBhAGMAaAAgAGIAYQBsAGUAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcAYgBhAGwAZQBkACcAIAB0AG8AIAB2AGEAcgBpAGEAYgBsAGUAIABzAHUAYgBzAGMAcgBpAHAAdABcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAbgBGAEYATwBEAGMAXABuAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAEYATwBEAF8AYwBiAGEAbABlAGQALAAgAEYARgBPAEQAXwBjAG8AdABoAGUAcgAsAFwAbgAgACAAIAAgAEYARgBPAEQAXwBjAGIAYQBsAGUAZAAgACsAIABGAEYATwBEAF8AYwBvAHQAaABlAHIAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMAfQAgAD0AIABGAEYATwBEAF8AewBjACwAYgBhAGwAZQBkAH0AIAArACAARgBGAE8ARABfAHsAYwAsAG8AdABoAGUAcgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAGIAYQBsAGUAZABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4AMQAuADEALgAyACwAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAGMAbwB0AGgAZQByAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAgAGIAeQAgAG8AdABoAGUAcgAgAG0AZQBhAG4AcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAB0AGgAaQBzACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAdQBzAGUAcgAtAGQAZQBmAGkAbgBlAGQAIAByAGUAcwBpAGQAdQBlACAAcgBlAG0AbwB2AGEAbAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABiAGEAbABpAG4AZwAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AEMASAA0AH0APQBcAG4AXABcAHMAdQBtAF8AewBjAH0AKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABDAEMAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBiAHUAcgBuAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAEMAQwBfAGMAIAA9ACAAYwBhAHIAYgBvAG4AIABtAGEAcwBzACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAdABoAGUAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARQBGAF8AQwBIADQAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAAoAGsAZwAgAEMASAA0AC8AawBnACAAQwBIADQAIABiAHUAcgBuAHQAKQBcAG4AQwBDAEgANAAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABtAGUAdABoAGEAbgBlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBiAHUAcgBuAGMALAAgAEMAQwBfAGMALAAgAEUARgBfAEMASAA0ACwAIABDAF8AQwBIADQALABcAG4AIAAgACAAIAAoAE0AXwBiAHUAcgBuAGMAIAAqACAAQwBDAF8AYwApACAAKgAgAEUARgBfAEMASAA0ACAAKgAgAEMAXwBDAEgANAAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAAQwBDAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGIAdQByAG4AYwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4ANAAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAQwBfAGMAXAAiACwAXAAiAGMAYQByAGIAbwBuACAAbQBhAHMAcwAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAEMASAA0AFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgAGYAcgBvAG0AIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAEgANAAgAGIAdQByAG4AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBDAEgANABcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXABuAEUATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAYwB9ACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGIAdQByAG4AYwAgAD0AIABtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcAG4ATgBDAF8AQQBHAGMAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAHQAaABlACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAEUARgBfAE4AMgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgByAG8AbQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAKABrAGcAIABOADIATwAvAGsAZwAgAE4AMgBPACAAYgB1AHIAbgB0ACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AYgB1AHIAbgBjACwAIABOAEMAXwBBAEcAYwAsACAARQBGAF8ATgAyAE8ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAGIAdQByAG4AYwAgACoAIABOAEMAXwBBAEcAYwApACAAKgAgAEUARgBfAE4AMgBPACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBiAHUAcgBuAGMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADQALgAxAC4AMQAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAHQAaABlACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACwAIABcACIAawBnACAATgAyAE8ALwBrAGcAIABOADIATwAgAGIAdQByAG4AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABcAG4ATQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwAgAGIAdQByAG4AdABcAG4ATQBfAGIAdQByAG4AYwBcAG4AawBnAFwAbgBNAF8AewBiAHUAcgBuACwAYwB9AD0AUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABTAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABaAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEYAXwB7AGMAfQBcAG4AUABfAGMAIAA9ACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcAG4AUgBfAEEARwBjACAAPQAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAvAGsAZwAgAGMAcgBvAHAAKQBcAG4AUwBfAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAcgBlAG0AYQBpAG4AaQBuAGcAIABhAHQAIABiAHUAcgBuAGkAbgBnACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEQATQBfAGMAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQApAFwAbgBaAF8AYwAgAD0AIABiAHUAcgBuAGkAbgBnACAAZQBmAGYAaQBjAGkAZQBuAGMAeQAgACgAcgBhAHQAaQBvACAAbwBmACAAZgB1AGUAbAAgAGIAdQByAG4AdAAgAHQAbwAgAGYAdQBlAGwAIABsAG8AYQBkACkAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBfAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAF8AYwAsACAAUgBfAEEARwBjACwAIABTAF8AYwAsACAARABNAF8AYwAsACAAWgBfAGMALAAgAEYAXwBjACwAXABuACAAIAAgACAAUABfAGMAIAAqACAAUgBfAEEARwBjACAAKgAgAFMAXwBjACAAKgAgAEQATQBfAGMAIAAqACAAWgBfAGMAIAAqACAARgBfAGMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIABiAHUAcgBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBiAHUAcgBuAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBiAHUAcgBuACwAYwB9AD0AUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABTAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABaAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEYAXwB7AGMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUALwBrAGcAIABjAHIAbwBwAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAYgB1AHIAbgBpAG4AZwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AXwBjAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBaAF8AYwBcACIALABcACIAYgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAIAAoAHIAYQB0AGkAbwAgAG8AZgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAIAB0AG8AIABmAHUAZQBsACAAbABvAGEAZAApACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGMAcgBvAHAAIABhAG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwALAAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHAAXABuAEUATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAYwB9AFwAXABzAHUAbQBfAHsAcAB9ACgATQBfAHsAbABlAGEAYwBoACwAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGwAZQBhAGMAaABjAHAAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAcAAgACgAawBnACAATgApAFwAbgBFAEYAXwBsAGUAYQBjAGgAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGwAZQBhAGMAaABjAHAALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAF8AbABlAGEAYwBoAGMAcAAgACoAIABFAEYAXwBsAGUAYQBjAGgAKQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYwByAG8AcAAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcAAoAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGwAZQBhAGMAaABjAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAGMAIABvAHIAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHAAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbABlAGEAYwBoAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAE0AXwBsAGUAYQBjAGgAYwBwAFwAbgBrAGcAIABOAFwAbgBNAF8AewBsAGUAYQBjAGgALABjAHAAfQA9AE0AXwB7AGMAcAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcARQBUAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgBNAF8AYwBwACAAPQAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgACgAawBnACAATgApAFwAbgBGAHIAYQBjAFcARQBUAGoAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEYAcgBhAGMATABFAEEAQwBIACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4AaQByACAAPQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBjAHAALAAgAEYAcgBhAGMAVwBFAFQAXwBqACwAIABGAHIAYQBjAEwARQBBAEMASAAsAFwAbgAgACAAIAAgAE0AXwBjAHAAIAAqACAARgByAGEAYwBXAEUAVABfAGoAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AbABlAGEAYwBoAGMAcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAbABlAGEAYwBoACwAYwBwAH0APQBNAF8AewBjAHAAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBXAEUAVABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwARQBBAEMASABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBjAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAIABmAHIAbwBtACAANgAuADEALgAxAC4AMQAgACgAMgApACAAYQBuAGQAIAA2AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAXwBqAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQAgAHoAIABhAG4AZAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGYAcgBvAG0AIABhAGwAbAAgAHAAYQBzAHQAdQByAGUAIAB0AHkAcABlAHMAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAEUATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAcAB9AFwAXABsAGUAZgB0ACgATQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgBpAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwB7ADEAMAB9AF4AewAtADMAfQBcAFwAcgBpAGcAaAB0ACkAXABuAE0AcAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcABhAHMAdAB1AHIAZQAgAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAE4AaQAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAgAGkAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAaQAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AcAAgAD0AIABQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcAG4AaQAgAD0AIABDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBwACwAIABFAEYAXwBOAGkALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAHAAIAAqACAARQBGAF8ATgBpACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMABeACgALQAzACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABmAHIAbwBtACAAYQBsAGwAIABwAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBzACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcABcAFwAbABlAGYAdAAoAE0AXwBwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AaQB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzAHsAMQAwAH0AXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIABwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AaQBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIABpAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALABcACIAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsAFwAIgBXAGUAdAAgAG8AcgAgAGQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAE0AcABcAG4AawBnACAATgBcAG4ATQBfAHAAIAA9ACAAKABBAF8AcAAgANcAKABZAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAIABcAFwAdABpAG0AZQBzACAAKAAxAC0AIABGAEYATwBEAF8AcAApACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAHAAfQApACAAKwAgACgAQQBfAHAAIABcAFwAdABpAG0AZQBzACAAKABZAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBwAH0AIABcAFwAdABpAG0AZQBzACAATgBDAF8AewBCAEcAcAB9ACkAXABuAEEAXwBwACAAPQAgAGEAcgBlAGEAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAG4AZQB3AGUAZAAgAG8AcgAgAHIAZQBtAG8AdgBlAGQAIAAoAGgAYQApAFwAbgBZAHAAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAHkAaQBlAGwAZAAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAKAB0ACAARABNAC8AaABhACkAXABuAE4AQwBBAEcAcAAgAD0AIABOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4AUgBfAEIARwBwACAAPQAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ATgBDAF8AQgBHAHAAIAA9ACAATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAbgBGAEYATwBEAHAAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHkAaQBlAGwAZAAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcAAsACAAWQBfAHAALAAgAEYARgBPAEQAXwBwACwAIABOAEMAXwBBAEcAcAAsACAAUgBfAEIARwBwACwAIABOAEMAXwBCAEcAcAAsAFwAbgAgACAAIAAgACgAQQBfAHAAIAAqACAAKABZAF8AcAAgACoAIAAxADAAXgAoAC0AMwApACkAIAAqACAAKAAxACAALQAgAEYARgBPAEQAXwBwACkAIAAqACAATgBDAF8AQQBHAHAAKQAgACsAIAAoAEEAXwBwACAAKgAgACgAWQBfAHAAIAAqACAAMQAwAF4AKAAtADMAKQApACAAKgAgAFIAXwBCAEcAcAAgACoAIABOAEMAXwBCAEcAcAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AcAAgAD0AIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACAARgBGAE8ARABfAHAAKQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBwAH0AKQAgACsAIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAcAB9ACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAHAAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcABcACIALABcACIAYQByAGUAYQAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAbgBlAHcAZQBkACAAbwByACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAF8AcABcACIALABcACIAYQB2AGUAcgBhAGcAZQAgAHkAaQBlAGwAZAAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAHQAIABEAE0ALwBoAGEAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQgBHAHAAXAAiACwAXAAiAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAHAAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAXwBwAFwAIgAsAFwAIgBhAHIAZQBhACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBuAGUAdwBlAGQAIABvAHIAIAByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAXwBwAFwAIgAsAFwAIgBhAHYAZQByAGEAZwBlACAAeQBpAGUAbABkACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAdAAgAEQATQAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEEARwBwAFwAIgAsAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBCAEcAcABcACIALABcACIAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcABcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEIARwBwAFwAIgAsAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAF8AcABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHkAaQBlAGwAZAAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBGAGUAcgB0AGkAbABpAHMAZQByAFAAcgBvAGQAdQBjAHQATABvAG8AawB1AHAAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABvAHQAYQBsAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQBwAHAAbABpAGUAZABBAGwAbABJAG4AZwByAGUAZABpAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAB0AEEAcABwAGwAaQBlAGQAQgB5AFMAbwB1AHIAYwBlAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AFMAYwBvAHAAZQAzAEUARgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABGAHIAYQBjAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQQBjAHQAaQB2AGUASQBuAGcAcgBlAGQAaQBlAG4AdABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAFAAdQByAHAAbwBzAGUAQQBuAGQAWQBpAGUAbABkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AQwB1AHMAdABvAG0AaQBzAGUAZABEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8AVABpAHQAbABlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -30986,30 +30974,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAJwBcACIAIAAmACAAcwBoACAAJgAgAFwAIgAnACEAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAJgAgAFwAIgAgAFwAIgAgACYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBQAHIAbwBkAHUAYwB0AEwAbwBvAGsAdQBwAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABQAHIAbwBkAHUAYwB0ACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5AEgAZQBhAGQAZQByAHMALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkAQwBvAGwAdQBtAG4ALABcAG4AIAAgACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAIAAgAFQAUgBJAE0AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEEAdAB0AHIAaQBiAHUAdABlAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkASABlAGEAZABlAHIAcwAsAFwAbgAgACAAIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAXAAiAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEALABcAG4AIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABbAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADIAXQAsAFwAbgAgACAAWwBMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwAXABuACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACAAPQAgAEwAbwBvAGsAdQBwAFQAYQByAGcAZQB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAEkAUwBPAE0ASQBUAFQARQBEACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADEALABcAG4AIAAgACAAIAAgACAALQAtACgAXABuACAAIAAgACAAIAAgACAAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAgAD0AIABMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAyAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACAAKgAgAGMAcgBpAHQAZQByAGkAYQAyACAAKgAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0ACwAXABuACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAXABuACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0AFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEEAcABwAGwAaQBlAGQAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADYAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANABcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA1AFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA1AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA0ACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA0AFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANgAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANgBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQAgAD0AIABcACIAXAAiACwAXABuACAAIAAgACAAIAAgAFwAIgBHAGwAbwBiAGEAbABcACIALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAXABuACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAgACsAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA0ACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADQALABcAG4AIAAgACAAIAAgACAAIAAgAFMAbwB1AHIAYwBlACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADUALABcAG4AIAAgACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANQAsAFwAbgAgACAAIAAgACAAIAAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABTAG8AdQByAGMAZQBcAG4AIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAIAArACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgAsAFwAbgAgACAAIAAgACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAXABuACAAIAAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBHAGUAdABTAGMAbwBwAGUAMwBFAEYAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgAFMAYwBvAHAAZQAzAEEAcgByAGEAeQAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAUwBvAHUAcgBjAGUALABcAG4AIAAgAFMAbwB1AHIAYwBlAFIAbwB3ACwAXABuACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIABTAGMAbwBwAGUAMwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEMAbwBsAHUAbQBuACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAE0AQQBUAEMASAAoAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAIAAgACAAIABTAG8AdQByAGMAZQBSAG8AdwAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABBAHIAcgBhAHkALABcAG4AIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQwBvAGwAdQBtAG4ALABcAG4AIAAgAEUAbABlAG0AZQBuAHQAUgBvAHcALABcAG4AIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAATQBBAFQAQwBIACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsAFwAbgAgACAAIAAgACAAIAAwAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABNAEEAVABDAEgAKABcAG4AIAAgACAAIAAgACAARQBsAGUAbQBlAG4AdAAsAFwAbgAgACAAIAAgACAAIABFAGwAZQBtAGUAbgB0AFIAbwB3ACwAXABuACAAIAAgACAAIAAgADAAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQQBjAHQAaQB2AGUASQBuAGcAcgBlAGQAaQBlAG4AdABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALABcAG4AIAAgACAAIAAoAFwAbgAgACAAIAAgACAAIABJAEYAKABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABVAG4AaQB0ADEAIAA9ACAAXAAiAFAAZQByAGMAZQBuAHQAIABvAGYAIABwAHIAbwBkAHUAYwB0AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyACwAXABuACAAIAAgACAAKABcAG4AIAAgACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAVQBuAGkAdAAxACAAPQAgAFwAIgBQAGUAcgBjAGUAbgB0ACAAbwBmACAAcAByAG8AZAB1AGMAdABcACIALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAyACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMwAsAFwAbgAgACAAIAAgACgAXABuACAAIAAgACAAIAAgAEkARgAoAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFUAbgBpAHQAMQAgAD0AIABcACIAUABlAHIAYwBlAG4AdAAgAG8AZgAgAHAAcgBvAGQAdQBjAHQAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACAAKgAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMALABcAG4AIAAgACAAIAAgACAAIAAgAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAIAAqACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMwAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAxACwAXABuACAAIAAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMQBcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApACAAKwAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAXABuACAAIAAgACAAIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMQAgAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBmAH0AKAAoAE0ATgBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagAsAE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AXwBqAGYAXABuAEUARgBfAGoATgAyAE8AXABuAEMAXwBOADIATwBcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABFAEYAXwBqAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAZgAgACoAIABFAEYAXwBqAE4AMgBPACAAKgAgAEMAXwBOADIATwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoALABOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAxAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBOADIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADEALgAxAC4AMgAgACgAMQApACgAMgApACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AXwBqAGYAXABuAGsAZwAgAE4AXABuAHsATQBOAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBOAF8AewBpAG4AbwByAGcAYQBuAGkAYwAsAGYAfQBcAG4AVABNAF8AagBmAFwAbgBGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBpAG4AbwByAGcAYQBuAGkAYwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAE4AXwBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AE0ATgB9AF8AewBqAGYAfQA9AFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYATgBfAHsAaQBuAG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALABcACIAdABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBOAF8AaQBuAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGkAcgByAGkAZwBhAHQAZQBkACAAbQBhAGkAegBlAFwAbgBFAEYAXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAE4AMgBPAFwAbgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcAG4ARQBGAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUALABOADIATwB9AD0AKAAtADAALgAxADQANwA0ACsAKAAwAC4AMAAwADYAMQBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AaQByAHIAaQBnAGEAdABlAGQAbQBhAGkAegBlAH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9AFwAbgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQAsAFwAbgAgACAAIAAgACgALQAwAC4AMQA0ADcANAAgACsAIAAoADAALgAwADAANgAxACAAKgAgAE4AXwBmAGoASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGYAagBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADIALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AGkAcgByAGkAZwBhAHQAZQBkAG0AYQBpAHoAZQAsAE4AMgBPAH0APQAoAC0AMAAuADEANAA3ADQAKwAoADAALgAwADAANgAxAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBpAHIAcgBpAGcAYQB0AGUAZABtAGEAaQB6AGUAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AZgBqAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABpAHIAcgBpAGcAYQB0AGUAZAAgAG0AYQBpAHoAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABnAHIAYQBpAG4AcwAgAGkAbgAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAbgBFAEYAXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4ATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBmAGoATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMALABcAG4AIAAgACAAIAAoADAALgAwADcAOAAxACAAKwAgACgAMAAuADAAMAA3ADUAIAAqACAATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwApACkAIAAqACAAMQAwACAAXgAgAC0AMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAZwByAGEAaQBuAHMAIABpAG4AIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgBqAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGEAcABwAGwAaQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AGYAagA9AG4AbwBuAGkAcgByAGkAZwBhAHQAZQBkAGcAcgBhAGkAbgBzACwATgAyAE8AfQA9ACgAMAAuADAANwA4ADEAKwAoADAALgAwADAANwA1AFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBuAG8AbgBpAHIAcgBpAGcAYQB0AGUAZABnAHIAYQBpAG4AcwB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGYAagBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBcACIALABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAaQBuACAAdABoAGUAIABnAHIAYQBpAG4AcwAgAGMAcgBvAHAAXAAiACwAIABcACIAawBnACAATgAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAbgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXABuAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABhAHAAcABsAGkAZQBkAFwAbgBFAEYAXwB7AGYAagA9AGMAbwB0AHQAbwBuACwATgAyAE8AfQA9AFwAXABtAGkAbgBcAFwAbABlAGYAdAAoACgAMAAuADAAMQBcAFwAdABpAG0AZQBzACgAMAAuADIAOQArADAALgAwADAANwBcAFwAdABpAG0AZQBzACgAKABlAF4AewAoADAALgAwADMANwBcAFwAdABpAG0AZQBzACAATgBfAHsAZgBqAD0AYwBvAHQAdABvAG4AfQApAH0ALQAxACkALwBOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9ACkAKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMgB9ACwAMAAuADAAMQA4ADMAXABcAHIAaQBnAGgAdAApAFwAbgBOAF8AZgBqAEMAbwB0AHQAbwBuAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGYAagBDAG8AdAB0AG8AbgAsAFwAbgAgACAAIAAgACgAMAAuADAAMQAgACoAIAAoADAALgAyADkAIAArACAAKAAgACAAKAAwAC4AMAAwADcAIAAqACAAKABFAFgAUAAoADAALgAwADMANwAgACoAIABOAF8AZgBqAEMAbwB0AHQAbwBuACkAIAAtACAAMQApACkAIAAvACAATgBfAGYAagBDAG8AdAB0AG8AbgAgACAAKQAgACkAKQAgACoAIAAxADAAIABeACAALQAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAG8AcgAgAGMAbwB0AHQAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwBmAGoAQwBvAHQAdABvAG4ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAZgBqAD0AYwBvAHQAdABvAG4ALABOADIATwB9AD0AKAAwAC4AMAAxACAAXABcAHQAaQBtAGUAcwAgACgAMAAuADIAOQAgACsAIABcAFwAZgByAGEAYwB7ADAALgAwADAANwAoAGUAXgB7ADAALgAwADMANwAgAFwAXAB0AGkAbQBlAHMAIABOAF8AewBmAGoAPQBjAG8AdAB0AG8AbgB9AH0ALQAxACkAfQB7AE4AXwB7AGYAagA9AGMAbwB0AHQAbwBuAH0AfQApACkAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADIAfQBcAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBmAGoAQwBvAHQAdABvAG4AXAAiACwAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGkAbgAgAHQAaABlACAAYwBvAHQAdABvAG4AIABjAHIAbwBwAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQA6ACAARgBlAHIAdABpAGwAaQBzAGUAcgAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUALgAxACAASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcAG4ARQBfAEMATwAyAFwAbgB0ACAAQwBPADIAXABuAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AVQBfAGoAZgBcAG4ARQBGAF8AdQByAGUAYQBDAE8AMgBcAG4AQwBfAEMATwAyAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAFUAXwBqAGYALAAgAEUARgBfAHUAcgBlAGEAQwBPADIALAAgAEMAXwBDAE8AMgAsAFwAbgAgACAAIAAgACgATQBVAF8AagBmACAAKgAgAEUARgBfAHUAcgBlAGEAQwBPADIAIAAqACAAQwBfAEMATwAyACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAsACAAdQByAGUAYQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMATwAyAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBVAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBPADIAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBVAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAAdQByAGUAYQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwB1AHIAZQBhAEMATwAyAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBhAHIAYgBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAIAB1AHIAZQBhAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAEMATwAyAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABjAGEAcgBiAG8AbgAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQBhAHMAcwAgAG8AZgAgAHUAcgBlAGEAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAFUAXwBqAGYAXABuAGsAZwAgAHUAcgBlAGEAXABuAHsATQBVAH0AXwB7AGoAZgB9AD0AVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgBVAF8AZgBcAG4AVABNAF8AagBmAFwAbgBGAFUAXwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARgBVAF8AZgAsAFwAbgAgACAAIAAgAFQATQBfAGoAZgAgACoAIABGAFUAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIAB1AHIAZQBhACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AVQBfAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIAB1AHIAZQBhAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBNAFUAfQBfAHsAagBmAH0APQBUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAFUAXwBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAF8AagBmAFwAIgAsAFwAIgB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBVAF8AZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdQByAGUAYQAgAGkAbgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALABcACIAawBnACAAdQByAGUAYQAvAGsAZwBcACIALAAgAFwAIgBMAG8AbwBrAHUAcABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMgAgAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8ATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8ALABpAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARQBGAF8ATgAyAE8AaQBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBpAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABFAEYAXwBOADIATwBpACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATgBTAG8AaQBsAF8AagBmACAAKgAgAEUARgBfAE4AMgBPAGkAIAAqACAAQwBfAE4AMgBPACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBOAFMAbwBpAGwAXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAaQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABhAG4AZAAgAGEAcQB1AGEAdABpAGMAIABzAHkAcwB0AGUAbQBzACAAaQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABpAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIATABvAG8AawB1AHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAXAAiAFcAZQB0ACAAbwByACAAZAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXABuAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARgBOAF8AbwByAGcAYQBuAGkAYwBmAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbwByAGcAYQBuAGkAYwBqAGYALAAgAEYATgBfAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAE0AXwBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABGAE4AXwBvAHIAZwBhAG4AaQBjAGYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AagBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwB7AGoAZgB9AD0ATQBfAHsAbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAE4AXwB7AG8AcgBnAGEAbgBpAGMALABmAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAG8AcgBnAGEAbgBpAGMAagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYATgBfAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIATwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMwAgAEwAaQBtAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAG4AZAAgAGQAbwBsAG8AbQBpAHQAZQAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8AbABpAG0AZQBcAG4AdAAgAEMATwAyAFwAbgBFAF8AewBsAGkAbQBlAH0APQBbACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwAaQBtAGUAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGkAbQBlAH0AKQArACgATQBfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEQAbwBsAFwAXAB0AGkAbQBlAHMAIABQAF8AewBkAG8AbAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGQAbwBsAH0AKQBdAFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAE8AMgB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBNAF8AbABpAG0AZQBcAG4ARgByAGEAYwBMAGkAbQBlAFwAbgBQAF8AbABpAG0AZQBcAG4ARQBGAF8AbABpAG0AZQBcAG4ARgByAGEAYwBEAG8AbABcAG4AUABfAGQAbwBsAFwAbgBFAEYAXwBkAG8AbABcAG4AQwBfAEMATwAyAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABpAG0AZQAsACAARgByAGEAYwBMAGkAbQBlACwAIABQAF8AbABpAG0AZQAsACAARQBGAF8AbABpAG0AZQAsACAARgByAGEAYwBEAG8AbAAsACAAUABfAGQAbwBsACwAIABFAEYAXwBkAG8AbAAsACAAQwBfAEMATwAyACwAXABuACAAIAAgACAAKAAoAE0AXwBsAGkAbQBlACAAKgAgAEYAcgBhAGMATABpAG0AZQAgACoAIABQAF8AbABpAG0AZQAgACoAIABFAEYAXwBsAGkAbQBlACkAIAArACAAKABNAF8AbABpAG0AZQAgACoAIABGAHIAYQBjAEQAbwBsACAAKgAgAFAAXwBkAG8AbAAgACoAIABFAEYAXwBkAG8AbAApACkAIAAqACAAQwBfAEMATwAyACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbABpAG0AZQAgAGEAbgBkACAAZABvAGwAbwBtAGkAdABlACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGwAaQBtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGwAaQBtAGUAfQA9AFsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABpAG0AZQBcAFwAdABpAG0AZQBzACAAUABfAHsAbABpAG0AZQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAaQBtAGUAfQApACsAKABNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARABvAGwAXABcAHQAaQBtAGUAcwAgAFAAXwB7AGQAbwBsAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZABvAGwAfQApAF0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMATwAyAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGwAaQBtAGUAXAAiACwAXAAiAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABsAGkAbQBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABsAGkAbQBlAHMAdABvAG4AZQAgACgAQwBhAEMATwAzACkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGwAaQBtAGUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgBhAGwAIABwAHUAcgBpAHQAeQAgAG8AZgAgAGwAaQBtAGUAcwB0AG8AbgBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAaQBtAGUAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGkAbQBlAHMAdABvAG4AZQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAXAAiACwAIABcACIAawBnACAAQwAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARABvAGwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAHMAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGQAbwBsAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABkAG8AbABvAG0AaQB0AGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZABvAGwAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAG8AbABvAG0AaQB0AGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlAFwAIgAsACAAXAAiAGsAZwAgAEMALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8AQwBPADIAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADQAIABJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGYAcgBvAG0AIABhAGwAbAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIABhAG4AZAAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAbgBFAF8AYQBkAGkAbgBvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAGkAbgBvAHIAZwBhAG4AaQBjAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYALAAgAEUARgBfAE4AMgBPAGoALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBhAGQAaQBuAG8AcgBnAGEAbgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAaQBuAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBqAH0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGYAfQAoACgATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANQAuADQALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBqAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsAFwAIgByAGEAaQBuAGYAYQBsAGwAIAByAGUAZwBpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcAG4AawBnACAATgBcAG4ATQBfAHsAdgBvAGwALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAZgB9AD0AewBNAE4AfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMARgBfAHsAZgB9AFwAbgBNAE4AXwBqAGYAXABuAEYAcgBhAGMARwBBAFMARgBfAGYAXABuAGoAXABuAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAsACAARgByAGEAYwBHAEEAUwBGAF8AZgAsAFwAbgAgACAAIAAgAE0ATgBfAGoAZgAgACoAIABGAHIAYQBjAEcAQQBTAEYAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AHYAbwBsACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAEYAXwB7AGYAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMARgBfAGYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAaABhAHQAIAB2AG8AbABhAHQAaQBsAGkAcwBlAHMAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AGEAZAAsAG8AcgBnAGEAbgBpAGMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcAG4ARQBGAF8ATgAyAE8AagBcAG4AQwBfAE4AMgBPAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmACwAIABFAEYAXwBOADIATwBqACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgAgACoAIABFAEYAXwBOADIATwBqACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGEAZABvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgA0AC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAYQBkACwAbwByAGcAYQBuAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB7AGoAfQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9ACgAKABNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwAsAGoAfQApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgA0AC4AMQAuADMAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AagBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAXAAiACwAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcAG4ATQBfAHYAbwBsAG8AcgBnAGEAbgBpAGMAagBmAFwAbgBrAGcAIABOAFwAbgBNAF8AewB2AG8AbAAsAG8AcgBnAGEAbgBpAGMALABqAGYAfQA9AE0ATgBTAG8AaQBsAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAF8AewBzAG8AaQBsAH0AXABuAE0ATgBTAG8AaQBsAF8AagBmAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBTAG8AaQBsAF8AagBmACwAIABGAHIAYQBjAEcAQQBTAE0AXwBzAG8AaQBsACwAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYAIAAqACAARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB2AG8AbABvAHIAZwBhAG4AaQBjAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANAAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAdgBvAGwALABvAHIAZwBhAG4AaQBjACwAagBmAH0APQBNAE4AUwBvAGkAbABfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAcwBvAGkAbAB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAFMAbwBpAGwAXwBqAGYAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADUALgAyAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AcwBvAGkAbABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABOACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwBcACIALAAgAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADUAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAC0AbwBmAGYAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXABuAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBmAGUAcgB0ACwAbABlAGEAYwBoAH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoACgATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0AKwBNAF8AewBsAGUAYQBjAGgALABvAHIAZwBhAG4AaQBjACwAagB9ACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAbgBNAF8AbABlAGEAYwBoAG8AcgBnAGEAbgBpAGMAagBcAG4ARQBGAF8AbABlAGEAYwBoAFwAbgBDAF8ATgAyAE8AXABuAGoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagAsACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAF8AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjAGoAIAArACAATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAKQAgACoAIABFAEYAXwBsAGUAYQBjAGgAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAYQBsAGwAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBmAGUAcgB0AGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGYAZQByAHQALABsAGUAYQBjAGgAfQA9AFwAXABzAHUAbQBfAHsAagB9ACgAKABNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQArAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4ANQAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGwAZQBhAGMAaABcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAE0AXwBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAagBcAG4AawBnACAATgBcAG4ATQBfAHsAbABlAGEAYwBoACwAaQBuAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAH0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBXAEUAVAAsAGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsATABFAEEAQwBIAH0AKQBcAG4ATQBOAF8AagBmAFwAbgBGAHIAYQBjAFcARQBUAGoAXABuAEYAcgBhAGMATABFAEEAQwBIAFwAbgBqAFwAbgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBmACwAIABGAHIAYQBjAFcARQBUAGoALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQBOAF8AagBmACAAKgAgAEYAcgBhAGMAVwBFAFQAagAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA1AC4ANQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABpAG4AbwByAGcAYQBuAGkAYwAsAGoAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AewBmAH0AXABcAGwAZQBmAHQAKAB7AE0ATgB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBmAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAegBcACIALABcACIAbABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcAG4ATQBfAGwAZQBhAGMAaABvAHIAZwBhAG4AaQBjAGoAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXwB7AGYAfQAoAHsATQBOAFMAbwBpAGwAfQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AFcARQBUACwAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAF8AewBMAEUAQQBDAEgAfQApAFwAbgBNAE4AUwBvAGkAbABfAGoAZgBcAG4ARgByAGEAYwBXAEUAVABqAFwAbgBGAHIAYQBjAEwARQBBAEMASABcAG4AagBcAG4AZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAFMAbwBpAGwAXwBqAGYALAAgAEYAcgBhAGMAVwBFAFQAagAsACAARgByAGEAYwBMAEUAQQBDAEgALABcAG4AIAAgACAAIABNAE4AUwBvAGkAbABfAGoAZgAgACoAIABGAHIAYQBjAFcARQBUAGoAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBsAGUAYQBjAGgAbwByAGcAYQBuAGkAYwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGwAZQBhAGMAaAAsAG8AcgBnAGEAbgBpAGMALABqAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHsAZgB9AFwAXABsAGUAZgB0ACgAewBNAE4AUwBvAGkAbAB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBfAHsAVwBFAFQALABqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAXwB7AEwARQBBAEMASAB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AUwBvAGkAbABfAGoAZgBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA1AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAagBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsAFwAIgBsAG8AYwBhAHQAaQBvAG4AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAHAAdQByAHAAbwBzAGUAIABhAG4AZAAgAHkAaQBlAGwAZABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABwAHUAcgBwAG8AcwBlACAAYQBuAGQAIAB5AGkAZQBsAGQAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAOAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAcgBwAG8AcwBlAFwAIgAsACAAXAAiAFAAZQByACAAaABlAGMAdABhAHIAZQAgAHUAbgBpAHQAXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAHQAZQByAG0AXAAiACwAIABcACIAaABhAHIAdgBlAHMAdAAgAGUAbgBkAHAAbwBpAG4AdABcACIALAAgAFwAIgBIAGEAcgB2AGUAcwB0ACAAdQBpAHQAXAAiACwAIABcACIAWQBpAGUAbABkACAAbgBvAHQAZQBcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAG4AbwB0AGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG4AbwB0AGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHMAaAAgAGcAcgBhAGkAbgAgAGMAcgBvAHAAXAAiACwAIABcACIAZwByAGEAaQBuAFwAIgAsACAAXAAiAHkAaQBlAGwAZABcACIALAAgAFwAIgBoAGEAcgB2AGUAcwB0AFwAIgAsACAAXAAiAGcAcgBhAGkAbgBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAGcAcgBhAGkAbgAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgByAG8AbQAgAHQAaABlACAAcABsAGEAbgB0AFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAcAByAG8AdgBpAGQAZQBkACAAZgByAG8AbQAgAGQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwBcACIALAAgAFwAIgBUAG8AdABhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAaQBzACAAdABoAGUAIAB0AG8AdABhAGwAIABnAHIAYQBpAG4AIABoAGEAcgB2AGUAcwB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcwBoACAAYwByAG8AcAAgAGYAbwByACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAeQBpAGUAbABkAFwAIgAsACAAXAAiAGgAYQByAHYAZQBzAHQAXAAiACwAIABcACIAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBZAGkAZQBsAGQAIABpAHMAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGgAYQByAHYAZQBzAHQAZQBkACAAZgBvAHIAIABoAGEAeQAvAHMAaQBsAGEAZwBlAFwAIgAsACAAXAAiAFIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAaQBzACAAMAAgAGEAcwBzAHUAbQBpAG4AZwAgAHQAaABlACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAaQBzACAAaABhAHIAdgBlAHMAdABlAGQAIABmAG8AcgAgAGgAYQB5AC8AcwBpAGwAYQBnAGUAXAAiACwAIABcACIAVABvAHQAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGkAcwAgAHQAaABlACAAdABvAHQAYQBsACAAdwBoAG8AbABlACAAcABsAGEAbgB0ACAAYgBpAG8AbQBhAHMAcwAgAGgAYQByAHYAZQBzAHQAZQBkACAAYQBzACAAaABhAHkALwBzAGkAbABhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAYgBpAG8AbQBhAHMAcwBcACIALAAgAFwAIgBtAGEAcwBzAFwAIgAsACAAXAAiAGUAbgBkACAAbwBmACAAYwByAG8AcAAgAGMAeQBjAGwAZQBcACIALAAgAFwAIgBhAGIAbwB2AGUAIABnAHIAbwB1AG4AZAAgAGIAaQBvAG0AYQBzAHMAXAAiACwAIABcACIAWQBpAGUAbABkACAAaQBzACAAdABoAGUAIAB3AGgAbwBsAGUAIABwAGwAYQBuAHQAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIALAAgAFwAIgBSAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGkAcwAgADEAIABhAHMAcwB1AG0AaQBuAGcAIAB0AGgAZQAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGkAcwAgAGsAZQBwAHQAIABhAHMAIABjAG8AdgBlAHIAIABjAHIAbwBwAFwAIgAsACAAXAAiAFQAbwB0AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABpAHMAIAB0AGgAZQAgAHQAbwB0AGEAbAAgAHcAaABvAGwAZQAgAHAAbABhAG4AdAAgAGIAaQBvAG0AYQBzAHMAIABrAGUAcAB0ACAAYQBzACAAYwBvAHYAZQByACAAYwByAG8AcABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADEAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4AMQA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADkALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAUgBlAHMAaQBkAHUAZQA6ACAAQwByAG8AcAAgAHIAYQB0AGkAbwBcACIALAAgAFwAIgBCAGUAbABvAHcALQBnAHIAbwB1AG4AZAA6ACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAEMAYQByAGIAbwBuACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAZAByAHkAIABtAGEAdAB0AGUAcgBcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkAFwAIgAsACAAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAdABpAG0AZQAgAG8AZgAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAQgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAFIAQQBHAGMAXAAiACwAIABcACIAUgBCAEcAYwBcACIALAAgAFwAIgBEAE0AYwBcACIALAAgAFwAIgBDAEMAYwBcACIALAAgAFwAIgBOAEMAQQBHAGMAXAAiACwAIABcACIATgBDAEIARwBjAFwAIgAsACAAXAAiAFMAYwBcACIALAAgAFwAIgBaAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAMQAuADUAMAAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOQAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIAAxAC4AMgA0ACwAIAAwAC4AMwAyACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADcALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AMwA5ACwAIAAwAC4AOAA1ACwAIAAwAC4ANAAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANwAsACAAMQAuADAALAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAMQAuADQAMgAsACAAMAAuADQAMwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgADEALgAzADEALAAgADAALgAxADYALAAgADAALgA4ADAALAAgADAALgA0ADIALAAgADAALgAwADAANwAsACAAMAAuADAAMQAwACwAIAAxAC4AMAAsACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIAAxAC4ANQAwACwAIAAwAC4AMgAyACwAIAAwAC4AOAAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADgALAAgADAALgAwADAANwAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgADEALgA1ADAALAAgADAALgA0ADIALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIAAxAC4ANAA2ACwAIAAwAC4AMwA2ACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADYALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgADEALgAzADcALAAgADAALgA1ADEALAAgADAALgA4ADcALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIAAwAC4AMwA0ACwAIAAwAC4ANAAzACwAIAAwAC4AMgA1ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAyADAALAAgADAALgAwADEAMAAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIAAxAC4AMAA3ACwAIAAwAC4AMgAwACwAIAAwAC4AOAAwACwAIAAwAC4ANAAyACwAIAAwAC4AMAAxADYALAAgADAALgAwADEANAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADIANQAsACAAMAAuADQANQAsACAAMAAuADIAMAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADcALAAgADEALgAwACwAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIAAxAC4AOQAwACwAIAAwAC4AMwAwACwAIAAwAC4AOQAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgADEALgA1ADAALAAgADAALgAyADkALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgADIALgAwADgALAAgADAALgAzADMALAAgADAALgA5ADYALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAMQAuADMANAAsACAAMAAuADMANwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgADEALgAwADAALAAgADAALgAyADIALAAgADAALgA4ADUALAAgADAALgA0ADAALAAgADAALgAwADAAOAAsACAAMAAuADAAMAA5ACwAIABcACIAbgAvAGEAXAAiACwAIABcACIAbgAvAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIAAxAC4ANQAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAJwBOAC8AQQAnACAAdgBhAGwAdQBlAHMAIABwAGEAcwBzAGUAZAAgAGEAcwAgAHoAZQByAG8AIABmAG8AcgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBzAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBDAHIAbwBwACAAYQB0AHQAcgBpAGIAdQB0AGUAcwAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAAKABGAEYATwBEAGMAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADIAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAHIAbwBwACAAYQB0AHQAcgBpAGIAdQB0AGUAcwAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAAKABGAEYATwBEAGMAKQBcACIAKQApADsAXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgAyADoAIABDAHIAbwBwACAAYQB0AHQAcgBpAGIAdQB0AGUAcwAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAAKABGAEYATwBEAGMAKQBcACIAKQApADsAXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAARgBGAE8ARABjAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAEEAbABsACAAcwB0AGEAdABlAHMAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAEEAbABsACAAcwB0AGEAdABlAHMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AQwB1AHMAdABvAG0AaQBzAGUAZABEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANAA0ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAYwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIATgBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAUwBwAGwAaQB0ACAAJwBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAJwAgAGkAbgB0AG8AIABpAG4AZABpAHYAaQBkAHUAYQBsACAAYwByAG8AcAAgAHQAeQBwAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAHMAdABhAHQAZQAuACAATABpAHMAdABlAGQAIABhAGwAbAAgAHMAdABhAHQAZQBzACAAZgBvAHIAIABTAHUAZwBhAHIAIABDAGEAbgBlACwAIAB3AGkAdABoACAAJwBOAC8AQQAnACAAZgBvAHIAIABzAHQAYQB0AGUAcwAgAHcAaABlAHIAZQAgAGkAdAAgAGkAcwAgAG4AbwB0ACAAZwByAG8AdwBuAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUABhAHMAdAB1AHIAZQAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAIABQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAOgAgAFAAYQBzAHQAdQByAGUAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAAWQBpAGUAbABkACAAKAB0ACAARABNACAAaABhACkAIABZAHAAXAAiACwAIABcACIAQgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAOgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAFIAQgBHAHAAXAAiACwAIABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABBAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAE4AQwBBAEcAcABcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAEIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAATgBDAEIARwBwAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AbgB1AGEAbAAgAGcAcgBhAHMAcwBcACIALAAgADQALgA0ADEALAAgADAALgA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAYQBzAHMAIABjAGwAbwB2AGUAcgAgAG0AaQB4AHQAdQByAGUAXAAiACwAIAA4AC4AMwA0ACwAIAAwAC4AOAAsACAAMAAuADAAMgA1ACwAIAAwAC4AMAAxADYALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATAB1AGMAZQByAG4AZQBcACIALAAgADgALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADEAOQAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABsAGUAZwB1AG0AZQBcACIALAAgADUALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADIAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgBlAG4AbgBpAGEAbAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAA4AC4AMwA1ACwAIAAwAC4AOAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADIALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAIgApACkAOwBcAG4AXABuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAdQByAG4AaQBuAGcAIABvAGYAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHIAZQBzAGkAZAB1AGUAcwAgAC0AIABFAEYAcwBcACIAKQApADsAXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAdgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIAA1AC4AMwAxADoAIABCAHUAcgBuAGkAbgBnACAAbwBmACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIAByAGUAcwBpAGQAdQBlAHMAIAAtACAARQBGAHMAXAAiACkAKQA7AFwAbgBcAG4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzACAAcwBwAGUAYwBpAGUAcwBcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAEUARgBnACAAKABHAGcAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAcwBwAGUAYwBpAGUAcwAvACAARwBnACAAZQBsAGUAbQBlAG4AdAAgAGkAbgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAKQBcACIALAAgAFwAIgBFAGwAZQBtAGUAbgB0AGEAbAAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAQwBnACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAwAC4AMAAwADMANQAsACAAXAAiADEANgAvADEAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADAALgAwADAANwA2ACwAIABcACIANAA0AC8AMgA4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4ATwB4AFwAIgAsACAAMAAuADIAMQAwADAALAAgAFwAIgA0ADYALwAxADQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAMAAuADAANwA4ADAALAAgAFwAIgAyADgALwAxADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAMAAuADAAMAA5ADEALAAgAFwAIgAxADQALwAxADIAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANAAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAIABUAGEAYgBsAGUAIAAxADEALgAxACAAWwAxACwAIABwAC4AIAAxADEAXQBcACIAKQA7AFwAbgBcAG4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAXAAiACwAIABcACIARQBGACAAaQAgAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ARQBcAG4AdAAgAE4AMgBPAFwAbgBFAD0AXABcAHMAdQBtAF8AewBjAH0AewBNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQB9AFwAbgBNAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIABjACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBnAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBjACwAIABFAEYAXwBOAGkALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAE0AXwBjACAAKgAgAEUARgBfAE4AaQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAHIAbwBwAHMAIABjACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAbABlAGYAdAAoAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAYwAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADEALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAF8ATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAIABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAVwBlAHQAIABvAHIAIABkAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAGMAXABuAGsAZwAgAE4AXABuAE0AXwB7AGMAfQA9ACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAYwB9AC0ARgBGAE8ARABfAHsAYwB9ACkAXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AKQArACgAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBCAEcAYwB9ACkAXABuAFAAYwAgAD0AIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACkAXABuAFIAQQBHAGMAIAA9ACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAFIAQgBHAGMAIAA9ACAAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAEYATwBEAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBEAE0AYwAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAKQBcAG4ATgBDAEEARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ATgBDAEIARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAXwBjACwAIABSAF8AQQBHAGMALAAgAEYAXwBjACwAIABGAEYATwBEAF8AYwAsACAARABNAF8AYwAsACAATgBDAF8AQQBHAGMALAAgAFIAXwBCAEcAYwAsACAATgBDAF8AQgBHAGMALABcAG4AIAAgACAAIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwAgACoAIAAoADEAIAAtACAARgBfAGMAIAAtACAARgBGAE8ARABfAGMAKQAgACoAIABEAE0AXwBjACAAKgAgAE4AQwBfAEEARwBjACkAIAArACAAKABQAF8AYwAgACoAIABSAF8AQQBHAGMAIAAqACAAUgBfAEIARwBjACAAKgAgAEQATQBfAGMAIAAqACAATgBDAF8AQgBHAGMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYwB9AD0AKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBjAH0ALQBGAEYATwBEAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQApACsAKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBjAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBfAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQgBHAGMAXAAiACwAXAAiAGIAZQBsAG8AdwAgAGcAcgBvAHUAbgBkAC0AcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAF8AYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AXwBjAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEEARwBjAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADAALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAXwBjAFwAIgAsAFwAIgBhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQQBHAGMAXAAiACwAXAAiAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBCAEcAYwBcACIALABcACIAYgBlAGwAbwB3ACAAZwByAG8AdQBuAGQALQByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlACAAZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAxAC4AMQAuADIAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAF8AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAF8AQgBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsAFwAIgBTAHQAYQB0AGUAIABvAHIAIAB0AGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcAG4ARgBGAE8ARABjAGIAYQBsAGUAZABcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4ARgBGAE8ARABfAHsAYwB9AD0AXABcAGYAcgBhAGMAewBCAFwAXAB0AGkAbQBlAHMAIABNAF8AewBCAH0AfQB7AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHACwAYwB9AH0AXABuAEIAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBNAEIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAGUAYQBjAGgAIABiAGEAbABlACAAKABrAGcAKQBcAG4AUABjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcAG4AUgBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABCACwAIABNAF8AQgAsACAAUABfAGMALAAgAFIAXwBBAEcAYwAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAoAEIAIAAqACAATQBfAEIAKQAgAC8AIAAoAFAAXwBjACAAKgAgAFIAXwBBAEcAYwApACwAIAAwACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjACwAIABjAGEAbABjAHUAbABhAHQAZQBkACAAdwBoAGUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAYQByAGUAIABiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADEALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMALABiAGEAbABlAGQAfQA9AFwAXABmAHIAYQBjAHsAQgBcAFwAdABpAG0AZQBzACAATQBfAHsAQgB9AH0AewBQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwAsAGMAfQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBcACIALABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBCAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAZQBhAGMAaAAgAGIAYQBsAGUAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABfAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcAYgBhAGwAZQBkACcAIAB0AG8AIAB2AGEAcgBpAGEAYgBsAGUAIABzAHUAYgBzAGMAcgBpAHAAdABcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjAFwAbgBGAEYATwBEAGMAXABuAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAEYATwBEAF8AYwBiAGEAbABlAGQALAAgAEYARgBPAEQAXwBjAG8AdABoAGUAcgAsAFwAbgAgACAAIAAgAEYARgBPAEQAXwBjAGIAYQBsAGUAZAAgACsAIABGAEYATwBEAF8AYwBvAHQAaABlAHIAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYARgBPAEQAXwB7AGMAfQAgAD0AIABGAEYATwBEAF8AewBjACwAYgBhAGwAZQBkAH0AIAArACAARgBGAE8ARABfAHsAYwAsAG8AdABoAGUAcgB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAXwBjAGIAYQBsAGUAZABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4AMQAuADEALgAyACwAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAGMAbwB0AGgAZQByAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAgAGIAeQAgAG8AdABoAGUAcgAgAG0AZQBhAG4AcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAB0AGgAaQBzACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAdQBzAGUAcgAtAGQAZQBmAGkAbgBlAGQAIAByAGUAcwBpAGQAdQBlACAAcgBlAG0AbwB2AGEAbAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABiAGEAbABpAG4AZwAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AEMASAA0AH0APQBcAG4AXABcAHMAdQBtAF8AewBjAH0AKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABDAEMAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AXwBiAHUAcgBuAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAEMAQwBfAGMAIAA9ACAAYwBhAHIAYgBvAG4AIABtAGEAcwBzACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAdABoAGUAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARQBGAF8AQwBIADQAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAAoAGsAZwAgAEMASAA0AC8AawBnACAAQwBIADQAIABiAHUAcgBuAHQAKQBcAG4AQwBDAEgANAAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABtAGUAdABoAGEAbgBlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBiAHUAcgBuAGMALAAgAEMAQwBfAGMALAAgAEUARgBfAEMASAA0ACwAIABDAF8AQwBIADQALABcAG4AIAAgACAAIAAoAE0AXwBiAHUAcgBuAGMAIAAqACAAQwBDAF8AYwApACAAKgAgAEUARgBfAEMASAA0ACAAKgAgAEMAXwBDAEgANAAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAAQwBDAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGIAdQByAG4AYwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4ANAAuADEALgAxACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAQwBfAGMAXAAiACwAXAAiAGMAYQByAGIAbwBuACAAbQBhAHMAcwAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAEMASAA0AFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgAGYAcgBvAG0AIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAEgANAAgAGIAdQByAG4AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBDAEgANABcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXABuAEUATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAYwB9ACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGIAdQByAG4AYwAgAD0AIABtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcAG4ATgBDAF8AQQBHAGMAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAHQAaABlACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAEUARgBfAE4AMgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgByAG8AbQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAKABrAGcAIABOADIATwAvAGsAZwAgAE4AMgBPACAAYgB1AHIAbgB0ACkAXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AYgB1AHIAbgBjACwAIABOAEMAXwBBAEcAYwAsACAARQBGAF8ATgAyAE8ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAGIAdQByAG4AYwAgACoAIABOAEMAXwBBAEcAYwApACAAKgAgAEUARgBfAE4AMgBPACAAKgAgAEMAXwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBiAHUAcgBuAGMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANgAuADQALgAxAC4AMQAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAHQAaABlACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACwAIABcACIAawBnACAATgAyAE8ALwBrAGcAIABOADIATwAgAGIAdQByAG4AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABcAG4ATQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwAgAGIAdQByAG4AdABcAG4ATQBfAGIAdQByAG4AYwBcAG4AawBnAFwAbgBNAF8AewBiAHUAcgBuACwAYwB9AD0AUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABTAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABaAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEYAXwB7AGMAfQBcAG4AUABfAGMAIAA9ACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcAG4AUgBfAEEARwBjACAAPQAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAvAGsAZwAgAGMAcgBvAHAAKQBcAG4AUwBfAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAcgBlAG0AYQBpAG4AaQBuAGcAIABhAHQAIABiAHUAcgBuAGkAbgBnACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEQATQBfAGMAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQApAFwAbgBaAF8AYwAgAD0AIABiAHUAcgBuAGkAbgBnACAAZQBmAGYAaQBjAGkAZQBuAGMAeQAgACgAcgBhAHQAaQBvACAAbwBmACAAZgB1AGUAbAAgAGIAdQByAG4AdAAgAHQAbwAgAGYAdQBlAGwAIABsAG8AYQBkACkAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBfAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAF8AYwAsACAAUgBfAEEARwBjACwAIABTAF8AYwAsACAARABNAF8AYwAsACAAWgBfAGMALAAgAEYAXwBjACwAXABuACAAIAAgACAAUABfAGMAIAAqACAAUgBfAEEARwBjACAAKgAgAFMAXwBjACAAKgAgAEQATQBfAGMAIAAqACAAWgBfAGMAIAAqACAARgBfAGMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIABiAHUAcgBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBiAHUAcgBuAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBiAHUAcgBuACwAYwB9AD0AUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABTAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABaAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEYAXwB7AGMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAF8AYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUALwBrAGcAIABjAHIAbwBwAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAYgB1AHIAbgBpAG4AZwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AXwBjAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwBcACIALAAgAFwAIgBrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBaAF8AYwBcACIALABcACIAYgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAIAAoAHIAYQB0AGkAbwAgAG8AZgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAIAB0AG8AIABmAHUAZQBsACAAbABvAGEAZAApACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGMAcgBvAHAAIABhAG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwALAAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHAAXABuAEUATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAYwB9AFwAXABzAHUAbQBfAHsAcAB9ACgATQBfAHsAbABlAGEAYwBoACwAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcAG4ATQBfAGwAZQBhAGMAaABjAHAAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAcAAgACgAawBnACAATgApAFwAbgBFAEYAXwBsAGUAYQBjAGgAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBfAGwAZQBhAGMAaABjAHAALAAgAEUARgBfAGwAZQBhAGMAaAAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAF8AbABlAGEAYwBoAGMAcAAgACoAIABFAEYAXwBsAGUAYQBjAGgAKQAgACoAIABDAF8ATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYwByAG8AcAAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcAAoAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGwAZQBhAGMAaABjAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAGMAIABvAHIAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHAAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADYALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbABlAGEAYwBoAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAE0AXwBsAGUAYQBjAGgAYwBwAFwAbgBrAGcAIABOAFwAbgBNAF8AewBsAGUAYQBjAGgALABjAHAAfQA9AE0AXwB7AGMAcAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcARQBUAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgBNAF8AYwBwACAAPQAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgACgAawBnACAATgApAFwAbgBGAHIAYQBjAFcARQBUAGoAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEYAcgBhAGMATABFAEEAQwBIACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4AaQByACAAPQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBjAHAALAAgAEYAcgBhAGMAVwBFAFQAXwBqACwAIABGAHIAYQBjAEwARQBBAEMASAAsAFwAbgAgACAAIAAgAE0AXwBjAHAAIAAqACAARgByAGEAYwBXAEUAVABfAGoAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AbABlAGEAYwBoAGMAcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAbABlAGEAYwBoACwAYwBwAH0APQBNAF8AewBjAHAAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBXAEUAVABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEwARQBBAEMASABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBjAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAIABmAHIAbwBtACAANgAuADEALgAxAC4AMQAgACgAMgApACAAYQBuAGQAIAA2AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAXwBqAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQAgAHoAIABhAG4AZAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAHIAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGYAcgBvAG0AIABhAGwAbAAgAHAAYQBzAHQAdQByAGUAIAB0AHkAcABlAHMAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAEUATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAcAB9AFwAXABsAGUAZgB0ACgATQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgBpAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwB7ADEAMAB9AF4AewAtADMAfQBcAFwAcgBpAGcAaAB0ACkAXABuAE0AcAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcABhAHMAdAB1AHIAZQAgAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAE4AaQAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAgAGkAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAaQAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AcAAgAD0AIABQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcAG4AaQAgAD0AIABDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBwACwAIABFAEYAXwBOAGkALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBfAHAAIAAqACAARQBGAF8ATgBpACkAIAAqACAAQwBfAE4AMgBPACAAKgAgADEAMABeACgALQAzACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABmAHIAbwBtACAAYQBsAGwAIABwAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBzACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcABcAFwAbABlAGYAdAAoAE0AXwBwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AaQB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzAHsAMQAwAH0AXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIABwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA2AC4AMgAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AaQBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIABpAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALABcACIAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsAFwAIgBXAGUAdAAgAG8AcgAgAGQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAE0AcABcAG4AawBnACAATgBcAG4ATQBfAHAAIAA9ACAAKABBAF8AcAAgANcAKABZAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAIABcAFwAdABpAG0AZQBzACAAKAAxAC0AIABGAEYATwBEAF8AcAApACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAHAAfQApACAAKwAgACgAQQBfAHAAIABcAFwAdABpAG0AZQBzACAAKABZAF8AcAAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBwAH0AIABcAFwAdABpAG0AZQBzACAATgBDAF8AewBCAEcAcAB9ACkAXABuAEEAXwBwACAAPQAgAGEAcgBlAGEAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAG4AZQB3AGUAZAAgAG8AcgAgAHIAZQBtAG8AdgBlAGQAIAAoAGgAYQApAFwAbgBZAHAAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAHkAaQBlAGwAZAAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAKAB0ACAARABNAC8AaABhACkAXABuAE4AQwBBAEcAcAAgAD0AIABOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4AUgBfAEIARwBwACAAPQAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ATgBDAF8AQgBHAHAAIAA9ACAATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAbgBGAEYATwBEAHAAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHkAaQBlAGwAZAAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAHAAIAA9ACAAUABhAHMAdAB1AHIAZQAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcAAsACAAWQBfAHAALAAgAEYARgBPAEQAXwBwACwAIABOAEMAXwBBAEcAcAAsACAAUgBfAEIARwBwACwAIABOAEMAXwBCAEcAcAAsAFwAbgAgACAAIAAgACgAQQBfAHAAIAAqACAAKABZAF8AcAAgACoAIAAxADAAXgAoAC0AMwApACkAIAAqACAAKAAxACAALQAgAEYARgBPAEQAXwBwACkAIAAqACAATgBDAF8AQQBHAHAAKQAgACsAIAAoAEEAXwBwACAAKgAgACgAWQBfAHAAIAAqACAAMQAwAF4AKAAtADMAKQApACAAKgAgAFIAXwBCAEcAcAAgACoAIABOAEMAXwBCAEcAcAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AcAAgAD0AIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACAARgBGAE8ARABfAHAAKQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBwAH0AKQAgACsAIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAcAB9ACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAHAAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcABcACIALABcACIAYQByAGUAYQAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAbgBlAHcAZQBkACAAbwByACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAF8AcABcACIALABcACIAYQB2AGUAcgBhAGcAZQAgAHkAaQBlAGwAZAAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwAFwAIgAsACAAXAAiAHQAIABEAE0ALwBoAGEAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBBAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAF8AQgBHAHAAXAAiACwAXAAiAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAXwBCAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AawBnACAARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBGAE8ARABfAHAAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAXwBwAFwAIgAsAFwAIgBhAHIAZQBhACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBuAGUAdwBlAGQAIABvAHIAIAByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAXwBwAFwAIgAsAFwAIgBhAHYAZQByAGEAZwBlACAAeQBpAGUAbABkACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAXAAiACwAIABcACIAdAAgAEQATQAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEEARwBwAFwAIgAsAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAXAAiACwAIABcACIAawBnACAATgAvAGsAZwAgAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXwBCAEcAcABcACIALABcACIAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAdABvACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvACAAZgBvAHIAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcABcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBfAEIARwBwAFwAIgAsAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBrAGcAIABEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAF8AcABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHkAaQBlAGwAZAAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBGAGUAcgB0AGkAbABpAHMAZQByAFAAcgBvAGQAdQBjAHQATABvAG8AawB1AHAAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABvAHQAYQBsAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQBwAHAAbABpAGUAZABBAGwAbABJAG4AZwByAGUAZABpAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAB0AEEAcABwAGwAaQBlAGQAQgB5AFMAbwB1AHIAYwBlAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AFMAYwBvAHAAZQAzAEUARgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABGAHIAYQBjAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQQBjAHQAaQB2AGUASQBuAGcAcgBlAGQAaQBlAG4AdABBAHAAcABsAGkAZQBkAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIASQByAHIAaQBnAGEAdABlAGQATQBhAGkAegBlAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEkAcgByAGkAZwBhAHQAZQBkAE0AYQBpAHoAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBJAHIAcgBpAGcAYQB0AGUAZABNAGEAaQB6AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIATgBvAG4ASQByAHIAaQBnAGEAdABlAGQARwByAGEAaQBuAHMASABpAGcAaABSAGEAaQBuAGYAYQBsAGwAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBOAG8AbgBJAHIAcgBpAGcAYQB0AGUAZABHAHIAYQBpAG4AcwBIAGkAZwBoAFIAYQBpAG4AZgBhAGwAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAE4AbwBuAEkAcgByAGkAZwBhAHQAZQBkAEcAcgBhAGkAbgBzAEgAaQBnAGgAUgBhAGkAbgBmAGEAbABsAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAyAF8AXwAzAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEMAbwB0AHQAbwBuAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADIAXwBfADMAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAQwBvAHQAdABvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMgBfAF8AMwBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBDAG8AdAB0AG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMAQwBPADIALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAEMATwAyAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwBDAE8AMgAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMATgAyAE8ALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAE4AMgBPAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwBOADIATwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AQwBPADIARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAEMATwAyAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBDAE8AMgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAFYAbwBsAGEAdABpAGwAaQBzAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADEAXwBGAGUAcgB0AGkAbABpAHMAZQByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBOADIATwBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMQBfAEYAZQByAHQAaQBsAGkAcwBlAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAE4AMgBPAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARgBlAHIAdABpAGwAaQBzAGUAcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYATgAyAE8ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYALgBWAEUARQBSAEcAXwA1AF8ANQBfADEAXwAxAF8AXwAzAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAZQBhAGMAaABlAGQARgByAG8AbQBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAuAFYARQBFAFIARwBfADUAXwA1AF8AMQBfADEAXwBfADMAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABlAGEAYwBoAGUAZABGAHIAbwBtAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAC4AVgBFAEUAUgBHAF8ANQBfADUAXwAxAF8AMQBfAF8AMwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAGUAYQBjAGgAZQBkAEYAcgBvAG0ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABQAHUAcgBwAG8AcwBlAEEAbgBkAFkAaQBlAGwAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAFAAdQByAHAAbwBzAGUAQQBuAGQAWQBpAGUAbABkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAFQAaQB0AGwAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8ARABhAHQAYQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AQwB1AHMAdABvAG0AaQBzAGUAZABEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8AVABpAHQAbABlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBEAGEAdABhACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAQQBnAHIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwByAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAcgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31028,10 +31021,21 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>